--- a/data/trans_dic/IP31KM04_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM04_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,31%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>37,88; 55,37</t>
+          <t>40,11; 56,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,05; 59,4</t>
+          <t>37,43; 54,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42,6; 54,84</t>
+          <t>41,73; 53,23</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,55%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>40,22; 58,21</t>
+          <t>36,73; 54,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36,55; 55,65</t>
+          <t>41,13; 58,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40,8; 53,54</t>
+          <t>40,89; 53,76</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,19%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>27,58; 51,77</t>
+          <t>36,59; 60,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,57; 58,43</t>
+          <t>27,45; 50,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,36; 51,71</t>
+          <t>34,22; 51,4</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>42,48%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>38,82%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>22,32; 39,77</t>
+          <t>35,58; 49,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,74; 48,8</t>
+          <t>32,81; 45,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>28,46; 41,95</t>
+          <t>36,37; 45,52</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>39,32; 55,39</t>
+          <t>41,65; 61,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,08; 62,1</t>
+          <t>39,38; 54,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,38; 56,95</t>
+          <t>42,48; 55,48</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,6%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,83; 61,34</t>
+          <t>36,49; 58,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35,43; 56,96</t>
+          <t>39,9; 60,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41,22; 57,39</t>
+          <t>40,86; 56,26</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>45,48%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36,8; 46,58</t>
+          <t>42,98; 50,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,35; 50,43</t>
+          <t>41,09; 47,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41,26; 47,33</t>
+          <t>42,78; 48,17</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>69</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>47287</t>
+          <t>58753</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67813</t>
+          <t>46068</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115100</t>
+          <t>104821</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>38527; 56321</t>
+          <t>48616; 68558</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>56835; 80297</t>
+          <t>37559; 54436</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100919; 129907</t>
+          <t>92459; 117933</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>45754</t>
+          <t>41133</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42667</t>
+          <t>46977</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88422</t>
+          <t>88110</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>37561; 54367</t>
+          <t>33009; 49006</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34246; 52144</t>
+          <t>39242; 55538</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76345; 100178</t>
+          <t>75772; 99618</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19879</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28740</t>
+          <t>20172</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>48618</t>
+          <t>46585</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13814; 25930</t>
+          <t>20433; 33505</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>21551; 36423</t>
+          <t>14276; 26386</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38628; 58132</t>
+          <t>36913; 55435</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>104</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>69530</t>
+          <t>83828</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>88978</t>
+          <t>68567</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>158509</t>
+          <t>152394</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48115; 85717</t>
+          <t>70206; 96807</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>76010; 103776</t>
+          <t>57962; 79724</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>121864; 179643</t>
+          <t>136014; 170237</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>54574</t>
+          <t>73067</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>80176</t>
+          <t>53691</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>134749</t>
+          <t>126758</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>45419; 63981</t>
+          <t>60634; 88946</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>67101; 99031</t>
+          <t>45470; 62617</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>119279; 156595</t>
+          <t>110885; 144841</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>35368</t>
+          <t>30947</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>31729</t>
+          <t>35258</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67097</t>
+          <t>66206</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>28129; 42257</t>
+          <t>24031; 38542</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24456; 39317</t>
+          <t>28071; 42712</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56849; 79149</t>
+          <t>55662; 76644</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>427</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>399</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>427</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>272392</t>
+          <t>314141</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>340102</t>
+          <t>270733</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>612494</t>
+          <t>584874</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>237436; 300474</t>
+          <t>290413; 340373</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>310127; 369298</t>
+          <t>250770; 292167</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>568292; 651908</t>
+          <t>550092; 619401</t>
         </is>
       </c>
     </row>
